--- a/data/raw/sales/Week 24/Audio_Array/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 24/Audio_Array/Vendor Sales (SP-API).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,19 +543,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="I2" t="n">
-        <v>532046.04</v>
+        <v>633067.4399999999</v>
       </c>
       <c r="J2" t="n">
-        <v>246</v>
+        <v>294</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -675,13 +675,13 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>48292.39</v>
+        <v>54731.38</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1005,14 +1005,14 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13555.92</v>
+      </c>
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>10166.94</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1401,13 +1401,13 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>12706.8</v>
+        <v>21178</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1467,14 +1467,14 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>16944.9</v>
+      </c>
+      <c r="J16" t="n">
         <v>4</v>
       </c>
-      <c r="I16" t="n">
-        <v>13555.92</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>11944.08</v>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1599,19 +1599,19 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I18" t="n">
-        <v>32450</v>
+        <v>33550</v>
       </c>
       <c r="J18" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1628,19 +1628,19 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0BLKCDRNB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FBA76723</t>
+          <t>FBA76727</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AM-C20</t>
+          <t>AM-C24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1665,13 +1665,13 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2286.44</v>
+        <v>1355.08</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1694,19 +1694,19 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA76723</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1716,34 +1716,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>32521.92</v>
+        <v>2286.44</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1760,19 +1760,19 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1782,34 +1782,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>145</v>
+        <v>33</v>
       </c>
       <c r="I21" t="n">
-        <v>589707.26</v>
+        <v>44717.64</v>
       </c>
       <c r="J21" t="n">
-        <v>148</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1826,19 +1826,19 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1863,19 +1863,19 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="I22" t="n">
-        <v>20333.88</v>
+        <v>687314.01</v>
       </c>
       <c r="J22" t="n">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1892,19 +1892,19 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FBA77010</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI-04 Black</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1929,20 +1929,20 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>20333.88</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
-        <v>5197.46</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>1p Sales</t>
@@ -1958,19 +1958,19 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA77010</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1980,34 +1980,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AI-04 Black</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>9907.639999999999</v>
+        <v>5197.46</v>
       </c>
       <c r="J24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2024,19 +2024,19 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FBA78203</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2046,34 +2046,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RGB USB Microphone Kit - Tripod</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
-        <v>1694.07</v>
+        <v>11008.49</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2090,19 +2090,19 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FBA78925</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>XLR Dynamic Mic</t>
+          <t>RGB USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>3092.37</v>
+        <v>1694.07</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -2156,19 +2156,19 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBA78925</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2178,28 +2178,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Tripod</t>
+          <t>XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>4192.38</v>
+        <v>3092.37</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2222,19 +2222,19 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2244,34 +2244,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>XLR Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>71760.92</v>
+        <v>4192.38</v>
       </c>
       <c r="J28" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2288,19 +2288,19 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2325,20 +2325,20 @@
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="I29" t="n">
-        <v>5082.21</v>
+        <v>91332.08</v>
       </c>
       <c r="J29" t="n">
+        <v>25</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>1p Sales</t>
@@ -2354,19 +2354,19 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FBA78976</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2376,28 +2376,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Monitor Speakers Accessories</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monitor Speaker Stand Pair</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>15673.73</v>
+        <v>5082.21</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2420,19 +2420,19 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA78976</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2457,19 +2457,19 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>70828.86</v>
+        <v>15673.73</v>
       </c>
       <c r="J31" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2486,19 +2486,19 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FBA79009</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2508,35 +2508,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Monitor Speakers Accessories</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Monitor Speaker Stand Pair</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I32" t="n">
-        <v>4065.24</v>
+        <v>80487.33</v>
       </c>
       <c r="J32" t="n">
+        <v>25</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>2</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>1p Sales</t>
@@ -2552,19 +2552,19 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FBA79016</t>
+          <t>FBA79009</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AM-C3a</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2592,16 +2592,16 @@
         <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>2031.36</v>
+        <v>4065.24</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2618,19 +2618,19 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA79016</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2640,34 +2640,34 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C3a</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Boomarm</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>36002.6</v>
+        <v>2031.36</v>
       </c>
       <c r="J34" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2684,19 +2684,19 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2706,34 +2706,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>XLR Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>42356</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2750,19 +2750,19 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FBA79010</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2772,28 +2772,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>5972.04</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2816,19 +2816,19 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FBA77171</t>
+          <t>FBA79010</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2838,28 +2838,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AC-6XL</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>11631.33</v>
+        <v>5972.04</v>
       </c>
       <c r="J37" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2882,19 +2882,19 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FBA79064</t>
+          <t>FBA77171</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AC-6XL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2919,19 +2919,19 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="I38" t="n">
-        <v>2877.98</v>
+        <v>13957.6</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2948,19 +2948,19 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79064</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2970,34 +2970,34 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wireless Conference Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>233514.54</v>
+        <v>4316.96</v>
       </c>
       <c r="J39" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3014,19 +3014,19 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3036,34 +3036,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Wireless Conference Microphone</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="I40" t="n">
-        <v>26262.73</v>
+        <v>246732.34</v>
       </c>
       <c r="J40" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3080,19 +3080,19 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FBA79104</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3117,19 +3117,19 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I41" t="n">
-        <v>34130.52</v>
+        <v>31515.28</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3146,19 +3146,19 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79104</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3183,19 +3183,19 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I42" t="n">
-        <v>5927.97</v>
+        <v>39381.37</v>
       </c>
       <c r="J42" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3212,19 +3212,19 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3234,34 +3234,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Speaker Karaoke</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Microphone with Speaker</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>17129.65</v>
+        <v>5927.97</v>
       </c>
       <c r="J43" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3278,19 +3278,19 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3300,34 +3300,34 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Speaker Karaoke</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Microphone with Speaker</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I44" t="n">
-        <v>3982.2</v>
+        <v>19144.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3344,19 +3344,19 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FBA79108</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3366,34 +3366,34 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AM-W16</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>2286.44</v>
+        <v>3982.2</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -3410,19 +3410,19 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA79108</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3447,19 +3447,19 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2286.44</v>
+      </c>
+      <c r="J46" t="n">
         <v>3</v>
       </c>
-      <c r="I46" t="n">
-        <v>4319.5</v>
-      </c>
-      <c r="J46" t="n">
-        <v>4</v>
-      </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -3476,19 +3476,19 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3498,28 +3498,28 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>2922.88</v>
+        <v>4319.5</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -3542,19 +3542,19 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3564,28 +3564,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Condenser Mic with Boom Arm</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>63371.16</v>
+        <v>5845.76</v>
       </c>
       <c r="J48" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -3608,19 +3608,19 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3630,28 +3630,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Mic with Boom Arm</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="I49" t="n">
-        <v>4236.44</v>
+        <v>77773.67999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3674,19 +3674,19 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AA-19WL</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3711,13 +3711,13 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>4236.44</v>
+        <v>8472.879999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3740,19 +3740,19 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3762,34 +3762,34 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AA-19WL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>6100</v>
+        <v>4236.44</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3806,19 +3806,19 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3843,19 +3843,19 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3872,19 +3872,19 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3909,13 +3909,13 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1705.08</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -3938,19 +3938,19 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3960,28 +3960,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AM-C11 Pro</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>12525.8</v>
+        <v>1705.08</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -4004,19 +4004,19 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79653</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4026,34 +4026,34 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AM-C45 Pro</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>18274.55</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4070,19 +4070,19 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4092,34 +4092,34 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AM-C11 Pro</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>147441.53</v>
+        <v>12525.8</v>
       </c>
       <c r="J56" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4136,19 +4136,19 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4158,34 +4158,34 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="I57" t="n">
-        <v>2414.41</v>
+        <v>26396.54</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -4202,19 +4202,19 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4224,34 +4224,34 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sound Bar</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sound Bar</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I58" t="n">
-        <v>26418.6</v>
+        <v>171591.53</v>
       </c>
       <c r="J58" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -4268,19 +4268,19 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4290,34 +4290,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>172794.62</v>
+        <v>2414.41</v>
       </c>
       <c r="J59" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -4334,19 +4334,19 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4356,34 +4356,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Sound Bar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GB-02</t>
+          <t>Sound Bar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="I60" t="n">
-        <v>6523.72</v>
+        <v>26418.6</v>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -4400,19 +4400,19 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FBA79821</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4422,34 +4422,34 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UB-01</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>196511.53</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -4466,19 +4466,19 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FBA79824</t>
+          <t>FBA79825</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4498,24 +4498,24 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GB-01</t>
+          <t>GB-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>6523.72</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4532,19 +4532,19 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA79821</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>UB-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -4598,19 +4598,19 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA79824</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>GB-03</t>
+          <t>GB-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -4664,19 +4664,19 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FBK79009</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4686,28 +4686,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1355.08</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -4730,19 +4730,19 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4762,25 +4762,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UB-02</t>
+          <t>GB-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2668.64</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
         <v>3</v>
       </c>
-      <c r="I66" t="n">
-        <v>32624.57</v>
-      </c>
-      <c r="J66" t="n">
-        <v>2</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>1</v>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>1p Sales</t>
@@ -4796,19 +4796,19 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FBA79844</t>
+          <t>FBK79009</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4818,28 +4818,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PB-08 (AM-C1 + AI-04)</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1355.08</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -4862,19 +4862,19 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4884,34 +4884,34 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>UB-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>5761.02</v>
+        <v>32624.57</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4928,19 +4928,19 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79844</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4950,34 +4950,34 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AH-60-BL</t>
+          <t>PB-08 (AM-C1 + AI-04)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>8470.34</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -4994,19 +4994,19 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5016,28 +5016,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AH-60-RD</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>1694.07</v>
+        <v>5761.02</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -5060,19 +5060,19 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5082,28 +5082,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I71" t="n">
-        <v>6351.7</v>
+        <v>10164.4</v>
       </c>
       <c r="J71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -5126,19 +5126,19 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5148,34 +5148,34 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>59623.52</v>
+        <v>1694.07</v>
       </c>
       <c r="J72" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -5192,19 +5192,19 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5214,34 +5214,34 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I73" t="n">
-        <v>1902.53</v>
+        <v>8892.379999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -5258,19 +5258,19 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5280,34 +5280,34 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="I74" t="n">
-        <v>76263.56</v>
+        <v>67754</v>
       </c>
       <c r="J74" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -5324,19 +5324,19 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5346,28 +5346,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I75" t="n">
-        <v>5692.4</v>
+        <v>1902.53</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -5390,19 +5390,19 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FBA79908</t>
+          <t>FBA79904</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5422,24 +5422,24 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I76" t="n">
-        <v>16267.8</v>
+        <v>84737.28</v>
       </c>
       <c r="J76" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -5456,19 +5456,19 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FBA79906</t>
+          <t>FBA79905</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5488,18 +5488,18 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I77" t="n">
-        <v>10083.9</v>
+        <v>12481.08</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -5522,19 +5522,19 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79908</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5544,34 +5544,34 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AM-W47 Wired</t>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wired Voice Amplifier</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I78" t="n">
-        <v>12193.2</v>
+        <v>16267.8</v>
       </c>
       <c r="J78" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -5588,19 +5588,19 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79906</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5610,25 +5610,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AM-W47 Wireless</t>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wireless Voice Amplifier</t>
+          <t>PB-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>1609.32</v>
+        <v>20167.8</v>
       </c>
       <c r="J79" t="n">
         <v>1</v>
@@ -5654,19 +5654,19 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FBA79969</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5676,34 +5676,34 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>UB-03 (AM-S1 + AA-22)</t>
+          <t>AM-W47 Wired</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UB-03</t>
+          <t>Wired Voice Amplifier</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I80" t="n">
-        <v>10422.88</v>
+        <v>13209.3</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -5720,19 +5720,19 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5742,17 +5742,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>AM-W47 Wireless</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Wireless Voice Amplifier</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>2439.87</v>
+        <v>1609.32</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -5786,19 +5786,19 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79969</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5808,25 +5808,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>UB-03 (AM-S1 + AA-22)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>UB-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>10422.88</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
@@ -5852,19 +5852,19 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79957</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5874,34 +5874,34 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>19570.32</v>
+        <v>2439.87</v>
       </c>
       <c r="J83" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -5918,19 +5918,19 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5940,34 +5940,34 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>4 channels Mixer</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>137449.94</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -5984,19 +5984,19 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6006,35 +6006,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>10 channels mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
+        <v>8</v>
+      </c>
+      <c r="I85" t="n">
+        <v>22366.08</v>
+      </c>
+      <c r="J85" t="n">
+        <v>9</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
         <v>3</v>
       </c>
-      <c r="I85" t="n">
-        <v>26670.34</v>
-      </c>
-      <c r="J85" t="n">
-        <v>3</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>2</v>
-      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>1p Sales</t>
@@ -6050,19 +6050,19 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6082,24 +6082,24 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>4 channels Mixer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I86" t="n">
-        <v>60583.88</v>
+        <v>151427.9</v>
       </c>
       <c r="J86" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -6116,19 +6116,19 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6148,24 +6148,24 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>6 channels mixer</t>
+          <t>10 channels mixer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>17794.92</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -6182,19 +6182,19 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6219,19 +6219,19 @@
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I88" t="n">
-        <v>70330.50999999999</v>
+        <v>71599.14</v>
       </c>
       <c r="J88" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -6248,19 +6248,19 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FBA80016</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6270,34 +6270,34 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>6 channels mixer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>11522.03</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -6314,19 +6314,19 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6346,25 +6346,25 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
+        <v>13</v>
+      </c>
+      <c r="I90" t="n">
+        <v>91429.67</v>
+      </c>
+      <c r="J90" t="n">
+        <v>12</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
         <v>3</v>
       </c>
-      <c r="I90" t="n">
-        <v>24150</v>
-      </c>
-      <c r="J90" t="n">
-        <v>4</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>1p Sales</t>
@@ -6380,19 +6380,19 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FBA79981</t>
+          <t>FBA80016</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6402,34 +6402,34 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AK-61 Neo</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LED DIsplay</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I91" t="n">
-        <v>21182.2</v>
+        <v>11522.03</v>
       </c>
       <c r="J91" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -6446,19 +6446,19 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBA80007</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6468,17 +6468,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard White</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -6486,10 +6486,10 @@
         <v>3</v>
       </c>
       <c r="I92" t="n">
-        <v>10166.94</v>
+        <v>24150</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -6512,19 +6512,19 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FBA79982</t>
+          <t>FBA79981</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AK-61 Pro</t>
+          <t>AK-61 Neo</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6544,24 +6544,24 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
+          <t>61 Key Electronic Keyboard With LED DIsplay</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I93" t="n">
-        <v>13980.51</v>
+        <v>21182.2</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -6578,19 +6578,19 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBA79980</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6610,15 +6610,15 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard Black</t>
+          <t>37 Key Electronic Keyboard White</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I94" t="n">
-        <v>3388.98</v>
+        <v>10166.94</v>
       </c>
       <c r="J94" t="n">
         <v>3</v>
@@ -6644,19 +6644,19 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79982</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6666,34 +6666,34 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AK-61 Pro</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="I95" t="n">
-        <v>287248.32</v>
+        <v>27961.02</v>
       </c>
       <c r="J95" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -6710,19 +6710,19 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA79979</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6732,34 +6732,34 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>37 Key Electronic Keyboard Black</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>2710.16</v>
+        <v>3388.98</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -6776,19 +6776,19 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6798,34 +6798,34 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="I97" t="n">
-        <v>761.86</v>
+        <v>331733.88</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -6842,19 +6842,19 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FBA80002</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6864,28 +6864,28 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AM-W33 Pro</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Single UHF Wireless Microphone With Receiver</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>2880.51</v>
+        <v>2710.16</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -6908,19 +6908,19 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79996</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6930,17 +6930,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>04 channels Mixer</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -6948,16 +6948,16 @@
         <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>6777.96</v>
+        <v>1523.72</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -6974,19 +6974,19 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA80002</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6996,17 +6996,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>AM-W33 Pro</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>06 channels Mixer</t>
+          <t>Single UHF Wireless Microphone With Receiver</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -7014,7 +7014,7 @@
         <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>6665.71</v>
+        <v>2880.51</v>
       </c>
       <c r="J100" t="n">
         <v>1</v>
@@ -7040,7 +7040,139 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>B0GXP97CZG</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FBA80084</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BE-4</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Audio Mixer</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>04 channels Mixer</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>2</v>
+      </c>
+      <c r="I101" t="n">
+        <v>6777.96</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>2</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>24</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>B0GXPBHDRF</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>FBA80085</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Audio Mixer</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>06 channels Mixer</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>6665.71</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>1p Sales</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>24</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
